--- a/resources/table/enum.error.xlsx
+++ b/resources/table/enum.error.xlsx
@@ -1,12 +1,12 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21240" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="ERROR_CODE" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ERROR_CODE" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="181029" fullCalcOnLoad="1"/>
@@ -470,7 +470,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B78"/>
+  <dimension ref="A1:B79"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="13.5"/>
   <cols>
     <col width="35" bestFit="1" customWidth="1" style="1" min="1" max="1"/>
@@ -1168,93 +1168,103 @@
       </c>
     </row>
     <row r="70">
-      <c r="A70" t="inlineStr">
+      <c r="A70" s="0" t="inlineStr">
         <is>
           <t>CLAN_ALREADY_ALLIED</t>
         </is>
       </c>
-      <c r="B70" t="n">
+      <c r="B70" s="0" t="n">
         <v>69</v>
       </c>
     </row>
     <row r="71">
-      <c r="A71" t="inlineStr">
+      <c r="A71" s="0" t="inlineStr">
         <is>
           <t>CLAN_NOT_ALLIED</t>
         </is>
       </c>
-      <c r="B71" t="n">
+      <c r="B71" s="0" t="n">
         <v>70</v>
       </c>
     </row>
     <row r="72">
-      <c r="A72" t="inlineStr">
+      <c r="A72" s="0" t="inlineStr">
         <is>
           <t>CLAN_CANNOT_ALLY_SELF</t>
         </is>
       </c>
-      <c r="B72" t="n">
+      <c r="B72" s="0" t="n">
         <v>71</v>
       </c>
     </row>
     <row r="73">
-      <c r="A73" t="inlineStr">
+      <c r="A73" s="0" t="inlineStr">
         <is>
           <t>CLAN_ALREADY_ENEMY</t>
         </is>
       </c>
-      <c r="B73" t="n">
+      <c r="B73" s="0" t="n">
         <v>72</v>
       </c>
     </row>
     <row r="74">
-      <c r="A74" t="inlineStr">
+      <c r="A74" s="0" t="inlineStr">
         <is>
           <t>CLAN_NOT_ENEMY</t>
         </is>
       </c>
-      <c r="B74" t="n">
+      <c r="B74" s="0" t="n">
         <v>73</v>
       </c>
     </row>
     <row r="75">
-      <c r="A75" t="inlineStr">
+      <c r="A75" s="0" t="inlineStr">
         <is>
           <t>CLAN_CANNOT_ENEMY_SELF</t>
         </is>
       </c>
-      <c r="B75" t="n">
+      <c r="B75" s="0" t="n">
         <v>74</v>
       </c>
     </row>
     <row r="76">
-      <c r="A76" t="inlineStr">
+      <c r="A76" s="0" t="inlineStr">
         <is>
           <t>CLAN_CANNOT_ENEMY_ALLY</t>
         </is>
       </c>
-      <c r="B76" t="n">
+      <c r="B76" s="0" t="n">
         <v>75</v>
       </c>
     </row>
     <row r="77">
-      <c r="A77" t="inlineStr">
+      <c r="A77" s="0" t="inlineStr">
         <is>
           <t>CLAN_CANNOT_ALLY_ENEMY</t>
         </is>
       </c>
-      <c r="B77" t="n">
+      <c r="B77" s="0" t="n">
         <v>76</v>
       </c>
     </row>
     <row r="78">
-      <c r="A78" t="inlineStr">
+      <c r="A78" s="0" t="inlineStr">
         <is>
           <t>CLAN_TARGET_NOT_FOUND</t>
         </is>
       </c>
-      <c r="B78" t="n">
+      <c r="B78" s="0" t="n">
         <v>77</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="0" t="inlineStr">
+        <is>
+          <t>MARKETPLACE_REQUEST_EXPIRED</t>
+        </is>
+      </c>
+      <c r="B79" s="0" t="n">
+        <v>78</v>
       </c>
     </row>
   </sheetData>

--- a/resources/table/enum.error.xlsx
+++ b/resources/table/enum.error.xlsx
@@ -470,7 +470,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B79"/>
+  <dimension ref="A1:B80"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="13.5"/>
   <cols>
     <col width="35" bestFit="1" customWidth="1" style="1" min="1" max="1"/>
@@ -1267,6 +1267,16 @@
         <v>78</v>
       </c>
     </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>ACCOUNT_LOCKED</t>
+        </is>
+      </c>
+      <c r="B80" t="n">
+        <v>79</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/resources/table/enum.error.xlsx
+++ b/resources/table/enum.error.xlsx
@@ -470,7 +470,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B80"/>
+  <dimension ref="A1:B82"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="13.5"/>
   <cols>
     <col width="35" bestFit="1" customWidth="1" style="1" min="1" max="1"/>
@@ -1268,13 +1268,33 @@
       </c>
     </row>
     <row r="80">
-      <c r="A80" t="inlineStr">
+      <c r="A80" s="0" t="inlineStr">
         <is>
           <t>ACCOUNT_LOCKED</t>
         </is>
       </c>
-      <c r="B80" t="n">
+      <c r="B80" s="0" t="n">
         <v>79</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="0" t="inlineStr">
+        <is>
+          <t>GROUP_FULL_MEMBER</t>
+        </is>
+      </c>
+      <c r="B81" s="0" t="n">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>MAIL_BOX_FULL</t>
+        </is>
+      </c>
+      <c r="B82" t="n">
+        <v>81</v>
       </c>
     </row>
   </sheetData>

--- a/resources/table/enum.error.xlsx
+++ b/resources/table/enum.error.xlsx
@@ -470,7 +470,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B82"/>
+  <dimension ref="A1:B83"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="13.5"/>
   <cols>
     <col width="35" bestFit="1" customWidth="1" style="1" min="1" max="1"/>
@@ -1288,13 +1288,23 @@
       </c>
     </row>
     <row r="82">
-      <c r="A82" t="inlineStr">
+      <c r="A82" s="0" t="inlineStr">
         <is>
           <t>MAIL_BOX_FULL</t>
         </is>
       </c>
-      <c r="B82" t="n">
+      <c r="B82" s="0" t="n">
         <v>81</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>CLAN_FULL_MEMBER</t>
+        </is>
+      </c>
+      <c r="B83" t="n">
+        <v>82</v>
       </c>
     </row>
   </sheetData>

--- a/resources/table/enum.error.xlsx
+++ b/resources/table/enum.error.xlsx
@@ -470,7 +470,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B83"/>
+  <dimension ref="A1:B87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="13.5"/>
   <cols>
     <col width="35" bestFit="1" customWidth="1" style="1" min="1" max="1"/>
@@ -1298,13 +1298,53 @@
       </c>
     </row>
     <row r="83">
-      <c r="A83" t="inlineStr">
+      <c r="A83" s="0" t="inlineStr">
         <is>
           <t>CLAN_FULL_MEMBER</t>
         </is>
       </c>
-      <c r="B83" t="n">
+      <c r="B83" s="0" t="n">
         <v>82</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>STORAGE_BOX_NOT_FOUND</t>
+        </is>
+      </c>
+      <c r="B84" t="n">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>STORAGE_BOX_ALREADY_RECEIVED</t>
+        </is>
+      </c>
+      <c r="B85" t="n">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>STORAGE_BOX_EXPIRED</t>
+        </is>
+      </c>
+      <c r="B86" t="n">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>CLAN_CANNOT_KICK_MASTER</t>
+        </is>
+      </c>
+      <c r="B87" t="n">
+        <v>86</v>
       </c>
     </row>
   </sheetData>

--- a/resources/table/enum.error.xlsx
+++ b/resources/table/enum.error.xlsx
@@ -470,7 +470,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B87"/>
+  <dimension ref="A1:B88"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="13.5"/>
   <cols>
     <col width="35" bestFit="1" customWidth="1" style="1" min="1" max="1"/>
@@ -1308,43 +1308,53 @@
       </c>
     </row>
     <row r="84">
-      <c r="A84" t="inlineStr">
+      <c r="A84" s="0" t="inlineStr">
         <is>
           <t>STORAGE_BOX_NOT_FOUND</t>
         </is>
       </c>
-      <c r="B84" t="n">
+      <c r="B84" s="0" t="n">
         <v>83</v>
       </c>
     </row>
     <row r="85">
-      <c r="A85" t="inlineStr">
+      <c r="A85" s="0" t="inlineStr">
         <is>
           <t>STORAGE_BOX_ALREADY_RECEIVED</t>
         </is>
       </c>
-      <c r="B85" t="n">
+      <c r="B85" s="0" t="n">
         <v>84</v>
       </c>
     </row>
     <row r="86">
-      <c r="A86" t="inlineStr">
+      <c r="A86" s="0" t="inlineStr">
         <is>
           <t>STORAGE_BOX_EXPIRED</t>
         </is>
       </c>
-      <c r="B86" t="n">
+      <c r="B86" s="0" t="n">
         <v>85</v>
       </c>
     </row>
     <row r="87">
-      <c r="A87" t="inlineStr">
+      <c r="A87" s="0" t="inlineStr">
         <is>
           <t>CLAN_CANNOT_KICK_MASTER</t>
         </is>
       </c>
-      <c r="B87" t="n">
+      <c r="B87" s="0" t="n">
         <v>86</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="0" t="inlineStr">
+        <is>
+          <t>BIRTHDAY_LOCKED</t>
+        </is>
+      </c>
+      <c r="B88" s="0" t="n">
+        <v>87</v>
       </c>
     </row>
   </sheetData>
